--- a/storybook_meta.xlsx
+++ b/storybook_meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cohue/Desktop/Files/10000shelf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C6B48A-BE67-9145-9B02-59505EF95080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4AE24C-F60C-AD40-933F-F18DAAD8784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,27 @@
     <sheet name="storybooks_ai(all)" sheetId="1" r:id="rId2"/>
     <sheet name="storybooks_original" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">storybooks_ai!$A$1:$H$251</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4602" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4596" uniqueCount="1130">
   <si>
     <t>id</t>
   </si>
@@ -4273,6 +4288,252 @@
   </si>
   <si>
     <t>title_ori</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>초등학생</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>성인</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌봄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>센터를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배경으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청소년들과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어르신들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교감하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서로의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상처를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치유하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감동적인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>모험/판타지</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>역사/문화</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>아동</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -4889,7 +5150,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4903,6 +5164,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5309,7 +5588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5354,8 +5633,8 @@
       <c r="C2" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>683</v>
+      <c r="D2" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>702</v>
@@ -5380,8 +5659,8 @@
       <c r="C3" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>683</v>
+      <c r="D3" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>703</v>
@@ -5406,8 +5685,8 @@
       <c r="C4" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>685</v>
+      <c r="D4" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>704</v>
@@ -5429,11 +5708,11 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>683</v>
+      <c r="C5" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>705</v>
@@ -5456,7 +5735,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>688</v>
@@ -5484,8 +5763,8 @@
       <c r="C7" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>683</v>
+      <c r="D7" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>707</v>
@@ -5510,8 +5789,8 @@
       <c r="C8" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>691</v>
+      <c r="D8" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>708</v>
@@ -5536,8 +5815,8 @@
       <c r="C9" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>683</v>
+      <c r="D9" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>709</v>
@@ -5562,8 +5841,8 @@
       <c r="C10" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>694</v>
+      <c r="D10" t="s">
+        <v>1124</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>710</v>
@@ -5588,8 +5867,8 @@
       <c r="C11" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>691</v>
+      <c r="D11" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>711</v>
@@ -5614,8 +5893,8 @@
       <c r="C12" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>685</v>
+      <c r="D12" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>712</v>
@@ -5640,8 +5919,8 @@
       <c r="C13" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>691</v>
+      <c r="D13" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>713</v>
@@ -5666,8 +5945,8 @@
       <c r="C14" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>683</v>
+      <c r="D14" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>714</v>
@@ -5689,11 +5968,11 @@
       <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>685</v>
+      <c r="C15" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>715</v>
@@ -5718,8 +5997,8 @@
       <c r="C16" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>685</v>
+      <c r="D16" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>716</v>
@@ -5744,8 +6023,8 @@
       <c r="C17" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>685</v>
+      <c r="D17" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>717</v>
@@ -5770,11 +6049,11 @@
       <c r="C18" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>718</v>
+      <c r="D18" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1125</v>
       </c>
       <c r="F18" t="s">
         <v>56</v>
@@ -5793,8 +6072,8 @@
       <c r="B19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>697</v>
+      <c r="C19" s="5" t="s">
+        <v>1127</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>688</v>
@@ -5848,8 +6127,8 @@
       <c r="C21" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>699</v>
+      <c r="D21" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>721</v>
@@ -5874,8 +6153,8 @@
       <c r="C22" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>699</v>
+      <c r="D22" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>724</v>
@@ -5900,8 +6179,8 @@
       <c r="C23" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>691</v>
+      <c r="D23" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>725</v>
@@ -5952,8 +6231,8 @@
       <c r="C25" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>699</v>
+      <c r="D25" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>727</v>
@@ -5978,8 +6257,8 @@
       <c r="C26" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>694</v>
+      <c r="D26" t="s">
+        <v>1124</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>728</v>
@@ -6004,8 +6283,8 @@
       <c r="C27" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>694</v>
+      <c r="D27" t="s">
+        <v>1124</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>729</v>
@@ -6056,8 +6335,8 @@
       <c r="C29" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>699</v>
+      <c r="D29" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>731</v>
@@ -6082,8 +6361,8 @@
       <c r="C30" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>699</v>
+      <c r="D30" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>732</v>
@@ -6108,8 +6387,8 @@
       <c r="C31" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>699</v>
+      <c r="D31" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>733</v>
@@ -6134,8 +6413,8 @@
       <c r="C32" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>699</v>
+      <c r="D32" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>733</v>
@@ -6160,8 +6439,8 @@
       <c r="C33" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>699</v>
+      <c r="D33" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>734</v>
@@ -6186,8 +6465,8 @@
       <c r="C34" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>699</v>
+      <c r="D34" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>735</v>
@@ -6209,11 +6488,11 @@
       <c r="B35" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>683</v>
+      <c r="C35" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>736</v>
@@ -6238,8 +6517,8 @@
       <c r="C36" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>691</v>
+      <c r="D36" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>737</v>
@@ -6264,8 +6543,8 @@
       <c r="C37" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>691</v>
+      <c r="D37" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>738</v>
@@ -6290,8 +6569,8 @@
       <c r="C38" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>699</v>
+      <c r="D38" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>739</v>
@@ -6316,8 +6595,8 @@
       <c r="C39" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>691</v>
+      <c r="D39" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>740</v>
@@ -6342,8 +6621,8 @@
       <c r="C40" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>722</v>
+      <c r="D40" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>741</v>
@@ -6443,11 +6722,11 @@
       <c r="B44" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>683</v>
+      <c r="C44" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>743</v>
@@ -6472,8 +6751,8 @@
       <c r="C45" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>744</v>
+      <c r="D45" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>745</v>
@@ -6498,8 +6777,8 @@
       <c r="C46" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>685</v>
+      <c r="D46" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>746</v>
@@ -6524,8 +6803,8 @@
       <c r="C47" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>699</v>
+      <c r="D47" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>747</v>
@@ -6550,8 +6829,8 @@
       <c r="C48" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>699</v>
+      <c r="D48" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>748</v>
@@ -6576,8 +6855,8 @@
       <c r="C49" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>683</v>
+      <c r="D49" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>749</v>
@@ -6602,8 +6881,8 @@
       <c r="C50" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>744</v>
+      <c r="D50" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>750</v>
@@ -6628,8 +6907,8 @@
       <c r="C51" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>744</v>
+      <c r="D51" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>751</v>
@@ -6654,8 +6933,8 @@
       <c r="C52" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>699</v>
+      <c r="D52" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>752</v>
@@ -6680,8 +6959,8 @@
       <c r="C53" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>699</v>
+      <c r="D53" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>753</v>
@@ -6706,8 +6985,8 @@
       <c r="C54" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>699</v>
+      <c r="D54" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>754</v>
@@ -6732,8 +7011,8 @@
       <c r="C55" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>699</v>
+      <c r="D55" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>755</v>
@@ -6758,8 +7037,8 @@
       <c r="C56" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>699</v>
+      <c r="D56" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>756</v>
@@ -6784,8 +7063,8 @@
       <c r="C57" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>699</v>
+      <c r="D57" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>757</v>
@@ -6810,8 +7089,8 @@
       <c r="C58" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>699</v>
+      <c r="D58" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>758</v>
@@ -6836,8 +7115,8 @@
       <c r="C59" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>691</v>
+      <c r="D59" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>759</v>
@@ -6888,8 +7167,8 @@
       <c r="C61" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>691</v>
+      <c r="D61" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>761</v>
@@ -6911,11 +7190,11 @@
       <c r="B62" t="s">
         <v>172</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>685</v>
+      <c r="C62" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>762</v>
@@ -6937,8 +7216,8 @@
       <c r="B63" t="s">
         <v>175</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>697</v>
+      <c r="C63" s="5" t="s">
+        <v>1127</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>688</v>
@@ -6992,8 +7271,8 @@
       <c r="C65" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>691</v>
+      <c r="D65" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>765</v>
@@ -7018,8 +7297,8 @@
       <c r="C66" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>699</v>
+      <c r="D66" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>766</v>
@@ -7044,8 +7323,8 @@
       <c r="C67" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>691</v>
+      <c r="D67" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>767</v>
@@ -7070,8 +7349,8 @@
       <c r="C68" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>691</v>
+      <c r="D68" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>768</v>
@@ -7096,8 +7375,8 @@
       <c r="C69" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>685</v>
+      <c r="D69" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>769</v>
@@ -7119,11 +7398,11 @@
       <c r="B70" t="s">
         <v>196</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>699</v>
+      <c r="C70" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>770</v>
@@ -7145,11 +7424,11 @@
       <c r="B71" t="s">
         <v>1045</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>699</v>
+      <c r="C71" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>771</v>
@@ -7171,11 +7450,11 @@
       <c r="B72" t="s">
         <v>1046</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>699</v>
+      <c r="C72" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>772</v>
@@ -7200,8 +7479,8 @@
       <c r="C73" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>699</v>
+      <c r="D73" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>773</v>
@@ -7252,8 +7531,8 @@
       <c r="C75" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>722</v>
+      <c r="D75" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>775</v>
@@ -7278,8 +7557,8 @@
       <c r="C76" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>691</v>
+      <c r="D76" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>776</v>
@@ -7304,8 +7583,8 @@
       <c r="C77" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>722</v>
+      <c r="D77" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>777</v>
@@ -7330,8 +7609,8 @@
       <c r="C78" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>691</v>
+      <c r="D78" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>778</v>
@@ -7382,8 +7661,8 @@
       <c r="C80" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>722</v>
+      <c r="D80" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>780</v>
@@ -7408,8 +7687,8 @@
       <c r="C81" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>722</v>
+      <c r="D81" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>781</v>
@@ -7460,8 +7739,8 @@
       <c r="C83" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>722</v>
+      <c r="D83" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>783</v>
@@ -7486,8 +7765,8 @@
       <c r="C84" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>699</v>
+      <c r="D84" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>784</v>
@@ -7512,8 +7791,8 @@
       <c r="C85" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>699</v>
+      <c r="D85" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>785</v>
@@ -7538,8 +7817,8 @@
       <c r="C86" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>699</v>
+      <c r="D86" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>786</v>
@@ -7590,8 +7869,8 @@
       <c r="C88" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>683</v>
+      <c r="D88" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>788</v>
@@ -7616,8 +7895,8 @@
       <c r="C89" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>699</v>
+      <c r="D89" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>789</v>
@@ -7642,8 +7921,8 @@
       <c r="C90" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>699</v>
+      <c r="D90" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>790</v>
@@ -7692,10 +7971,10 @@
         <v>1031</v>
       </c>
       <c r="C92" t="s">
-        <v>1032</v>
+        <v>1126</v>
       </c>
       <c r="D92" t="s">
-        <v>699</v>
+        <v>1124</v>
       </c>
       <c r="E92" t="s">
         <v>1033</v>
@@ -7720,8 +7999,8 @@
       <c r="C93" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>683</v>
+      <c r="D93" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>792</v>
@@ -7746,8 +8025,8 @@
       <c r="C94" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>683</v>
+      <c r="D94" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>793</v>
@@ -7772,8 +8051,8 @@
       <c r="C95" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>699</v>
+      <c r="D95" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>794</v>
@@ -7798,8 +8077,8 @@
       <c r="C96" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>691</v>
+      <c r="D96" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>795</v>
@@ -7824,8 +8103,8 @@
       <c r="C97" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>699</v>
+      <c r="D97" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>796</v>
@@ -7850,8 +8129,8 @@
       <c r="C98" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>699</v>
+      <c r="D98" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>797</v>
@@ -7876,8 +8155,8 @@
       <c r="C99" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>699</v>
+      <c r="D99" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>798</v>
@@ -7902,8 +8181,8 @@
       <c r="C100" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>691</v>
+      <c r="D100" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>799</v>
@@ -7928,8 +8207,8 @@
       <c r="C101" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>691</v>
+      <c r="D101" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>799</v>
@@ -7954,8 +8233,8 @@
       <c r="C102" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>699</v>
+      <c r="D102" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>800</v>
@@ -8006,8 +8285,8 @@
       <c r="C104" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>699</v>
+      <c r="D104" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>802</v>
@@ -8032,8 +8311,8 @@
       <c r="C105" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>699</v>
+      <c r="D105" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>803</v>
@@ -8058,8 +8337,8 @@
       <c r="C106" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>699</v>
+      <c r="D106" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>804</v>
@@ -8084,8 +8363,8 @@
       <c r="C107" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>699</v>
+      <c r="D107" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>805</v>
@@ -8110,8 +8389,8 @@
       <c r="C108" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>744</v>
+      <c r="D108" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>806</v>
@@ -8136,8 +8415,8 @@
       <c r="C109" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>699</v>
+      <c r="D109" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>807</v>
@@ -8162,8 +8441,8 @@
       <c r="C110" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>699</v>
+      <c r="D110" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>807</v>
@@ -8188,8 +8467,8 @@
       <c r="C111" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>744</v>
+      <c r="D111" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>808</v>
@@ -8214,8 +8493,8 @@
       <c r="C112" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>683</v>
+      <c r="D112" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>809</v>
@@ -8240,8 +8519,8 @@
       <c r="C113" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>683</v>
+      <c r="D113" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>809</v>
@@ -8266,8 +8545,8 @@
       <c r="C114" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>699</v>
+      <c r="D114" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>810</v>
@@ -8318,8 +8597,8 @@
       <c r="C116" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>699</v>
+      <c r="D116" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>812</v>
@@ -8344,8 +8623,8 @@
       <c r="C117" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>683</v>
+      <c r="D117" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>813</v>
@@ -8370,8 +8649,8 @@
       <c r="C118" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>683</v>
+      <c r="D118" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>814</v>
@@ -8396,8 +8675,8 @@
       <c r="C119" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>699</v>
+      <c r="D119" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>815</v>
@@ -8422,8 +8701,8 @@
       <c r="C120" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>699</v>
+      <c r="D120" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>816</v>
@@ -8448,8 +8727,8 @@
       <c r="C121" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>699</v>
+      <c r="D121" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>817</v>
@@ -8474,8 +8753,8 @@
       <c r="C122" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>699</v>
+      <c r="D122" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>818</v>
@@ -8500,8 +8779,8 @@
       <c r="C123" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>699</v>
+      <c r="D123" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>819</v>
@@ -8526,8 +8805,8 @@
       <c r="C124" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>744</v>
+      <c r="D124" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>820</v>
@@ -8552,8 +8831,8 @@
       <c r="C125" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>699</v>
+      <c r="D125" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>821</v>
@@ -8578,8 +8857,8 @@
       <c r="C126" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>699</v>
+      <c r="D126" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>822</v>
@@ -8604,8 +8883,8 @@
       <c r="C127" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>699</v>
+      <c r="D127" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>823</v>
@@ -8630,8 +8909,8 @@
       <c r="C128" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>744</v>
+      <c r="D128" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>824</v>
@@ -8656,8 +8935,8 @@
       <c r="C129" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>744</v>
+      <c r="D129" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>825</v>
@@ -8682,8 +8961,8 @@
       <c r="C130" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>699</v>
+      <c r="D130" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>826</v>
@@ -8734,8 +9013,8 @@
       <c r="C132" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>744</v>
+      <c r="D132" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>828</v>
@@ -8760,8 +9039,8 @@
       <c r="C133" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>699</v>
+      <c r="D133" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>829</v>
@@ -8812,8 +9091,8 @@
       <c r="C135" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>699</v>
+      <c r="D135" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>831</v>
@@ -8838,8 +9117,8 @@
       <c r="C136" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>699</v>
+      <c r="D136" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>832</v>
@@ -8864,8 +9143,8 @@
       <c r="C137" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>744</v>
+      <c r="D137" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>833</v>
@@ -8890,8 +9169,8 @@
       <c r="C138" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D138" s="2" t="s">
-        <v>722</v>
+      <c r="D138" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>834</v>
@@ -8916,8 +9195,8 @@
       <c r="C139" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>699</v>
+      <c r="D139" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>835</v>
@@ -8942,8 +9221,8 @@
       <c r="C140" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>722</v>
+      <c r="D140" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>836</v>
@@ -8968,8 +9247,8 @@
       <c r="C141" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>699</v>
+      <c r="D141" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>837</v>
@@ -8994,8 +9273,8 @@
       <c r="C142" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>699</v>
+      <c r="D142" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>837</v>
@@ -9020,8 +9299,8 @@
       <c r="C143" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>699</v>
+      <c r="D143" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>838</v>
@@ -9046,8 +9325,8 @@
       <c r="C144" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>699</v>
+      <c r="D144" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>839</v>
@@ -9072,8 +9351,8 @@
       <c r="C145" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D145" s="2" t="s">
-        <v>744</v>
+      <c r="D145" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>840</v>
@@ -9098,8 +9377,8 @@
       <c r="C146" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>699</v>
+      <c r="D146" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>841</v>
@@ -9124,8 +9403,8 @@
       <c r="C147" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>699</v>
+      <c r="D147" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>842</v>
@@ -9150,8 +9429,8 @@
       <c r="C148" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>699</v>
+      <c r="D148" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>843</v>
@@ -9176,8 +9455,8 @@
       <c r="C149" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>699</v>
+      <c r="D149" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>844</v>
@@ -9202,8 +9481,8 @@
       <c r="C150" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>744</v>
+      <c r="D150" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>845</v>
@@ -9228,8 +9507,8 @@
       <c r="C151" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>744</v>
+      <c r="D151" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>846</v>
@@ -9254,8 +9533,8 @@
       <c r="C152" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>847</v>
+      <c r="D152" t="s">
+        <v>1124</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>848</v>
@@ -9280,8 +9559,8 @@
       <c r="C153" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>847</v>
+      <c r="D153" t="s">
+        <v>1124</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>848</v>
@@ -9306,8 +9585,8 @@
       <c r="C154" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>699</v>
+      <c r="D154" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>849</v>
@@ -9332,8 +9611,8 @@
       <c r="C155" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>699</v>
+      <c r="D155" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>850</v>
@@ -9358,8 +9637,8 @@
       <c r="C156" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>744</v>
+      <c r="D156" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>851</v>
@@ -9410,8 +9689,8 @@
       <c r="C158" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>699</v>
+      <c r="D158" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>853</v>
@@ -9436,8 +9715,8 @@
       <c r="C159" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>691</v>
+      <c r="D159" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>854</v>
@@ -9462,8 +9741,8 @@
       <c r="C160" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>691</v>
+      <c r="D160" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>855</v>
@@ -9514,8 +9793,8 @@
       <c r="C162" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>691</v>
+      <c r="D162" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>857</v>
@@ -9540,8 +9819,8 @@
       <c r="C163" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>699</v>
+      <c r="D163" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>858</v>
@@ -9566,8 +9845,8 @@
       <c r="C164" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>699</v>
+      <c r="D164" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>859</v>
@@ -9618,8 +9897,8 @@
       <c r="C166" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D166" s="2" t="s">
-        <v>744</v>
+      <c r="D166" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>861</v>
@@ -9644,8 +9923,8 @@
       <c r="C167" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D167" s="2" t="s">
-        <v>744</v>
+      <c r="D167" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>865</v>
@@ -9670,8 +9949,8 @@
       <c r="C168" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>699</v>
+      <c r="D168" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>862</v>
@@ -9696,8 +9975,8 @@
       <c r="C169" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>699</v>
+      <c r="D169" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>863</v>
@@ -9722,8 +10001,8 @@
       <c r="C170" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>722</v>
+      <c r="D170" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>864</v>
@@ -9748,8 +10027,8 @@
       <c r="C171" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>699</v>
+      <c r="D171" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>866</v>
@@ -9774,8 +10053,8 @@
       <c r="C172" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>699</v>
+      <c r="D172" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>867</v>
@@ -9800,8 +10079,8 @@
       <c r="C173" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D173" s="2" t="s">
-        <v>744</v>
+      <c r="D173" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>868</v>
@@ -9826,8 +10105,8 @@
       <c r="C174" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>699</v>
+      <c r="D174" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>869</v>
@@ -9852,8 +10131,8 @@
       <c r="C175" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D175" s="2" t="s">
-        <v>683</v>
+      <c r="D175" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>870</v>
@@ -9904,8 +10183,8 @@
       <c r="C177" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D177" s="2" t="s">
-        <v>699</v>
+      <c r="D177" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>872</v>
@@ -9956,8 +10235,8 @@
       <c r="C179" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D179" s="2" t="s">
-        <v>699</v>
+      <c r="D179" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>874</v>
@@ -9982,8 +10261,8 @@
       <c r="C180" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D180" s="2" t="s">
-        <v>699</v>
+      <c r="D180" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>875</v>
@@ -10008,8 +10287,8 @@
       <c r="C181" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>744</v>
+      <c r="D181" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>876</v>
@@ -10034,8 +10313,8 @@
       <c r="C182" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D182" s="2" t="s">
-        <v>699</v>
+      <c r="D182" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>877</v>
@@ -10086,8 +10365,8 @@
       <c r="C184" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>699</v>
+      <c r="D184" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>879</v>
@@ -10109,11 +10388,11 @@
       <c r="B185" t="s">
         <v>505</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>691</v>
+      <c r="C185" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>880</v>
@@ -10164,8 +10443,8 @@
       <c r="C187" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D187" s="2" t="s">
-        <v>699</v>
+      <c r="D187" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>882</v>
@@ -10213,11 +10492,11 @@
       <c r="B189" t="s">
         <v>517</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>683</v>
+      <c r="C189" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>884</v>
@@ -10239,11 +10518,11 @@
       <c r="B190" t="s">
         <v>520</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>744</v>
+      <c r="C190" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>885</v>
@@ -10268,8 +10547,8 @@
       <c r="C191" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D191" s="2" t="s">
-        <v>699</v>
+      <c r="D191" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>886</v>
@@ -10294,8 +10573,8 @@
       <c r="C192" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D192" s="2" t="s">
-        <v>744</v>
+      <c r="D192" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>887</v>
@@ -10320,8 +10599,8 @@
       <c r="C193" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D193" s="2" t="s">
-        <v>699</v>
+      <c r="D193" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>888</v>
@@ -10346,8 +10625,8 @@
       <c r="C194" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D194" s="2" t="s">
-        <v>683</v>
+      <c r="D194" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>889</v>
@@ -10372,8 +10651,8 @@
       <c r="C195" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>744</v>
+      <c r="D195" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>890</v>
@@ -10450,8 +10729,8 @@
       <c r="C198" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>744</v>
+      <c r="D198" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>893</v>
@@ -10473,11 +10752,11 @@
       <c r="B199" t="s">
         <v>547</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>683</v>
+      <c r="C199" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>894</v>
@@ -10502,8 +10781,8 @@
       <c r="C200" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>744</v>
+      <c r="D200" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>895</v>
@@ -10528,8 +10807,8 @@
       <c r="C201" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D201" s="2" t="s">
-        <v>744</v>
+      <c r="D201" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>896</v>
@@ -10554,8 +10833,8 @@
       <c r="C202" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>699</v>
+      <c r="D202" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>897</v>
@@ -10580,8 +10859,8 @@
       <c r="C203" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D203" s="2" t="s">
-        <v>699</v>
+      <c r="D203" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>898</v>
@@ -10606,8 +10885,8 @@
       <c r="C204" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D204" s="2" t="s">
-        <v>699</v>
+      <c r="D204" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>899</v>
@@ -10632,8 +10911,8 @@
       <c r="C205" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D205" s="2" t="s">
-        <v>744</v>
+      <c r="D205" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>900</v>
@@ -10658,8 +10937,8 @@
       <c r="C206" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D206" s="2" t="s">
-        <v>683</v>
+      <c r="D206" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>901</v>
@@ -10684,8 +10963,8 @@
       <c r="C207" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>744</v>
+      <c r="D207" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>902</v>
@@ -10710,8 +10989,8 @@
       <c r="C208" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D208" s="2" t="s">
-        <v>683</v>
+      <c r="D208" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>903</v>
@@ -10736,8 +11015,8 @@
       <c r="C209" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D209" s="2" t="s">
-        <v>744</v>
+      <c r="D209" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>904</v>
@@ -10762,8 +11041,8 @@
       <c r="C210" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D210" s="2" t="s">
-        <v>699</v>
+      <c r="D210" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>941</v>
@@ -10788,8 +11067,8 @@
       <c r="C211" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D211" s="2" t="s">
-        <v>699</v>
+      <c r="D211" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>905</v>
@@ -10814,8 +11093,8 @@
       <c r="C212" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>699</v>
+      <c r="D212" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>906</v>
@@ -10840,8 +11119,8 @@
       <c r="C213" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D213" s="2" t="s">
-        <v>683</v>
+      <c r="D213" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>907</v>
@@ -10866,8 +11145,8 @@
       <c r="C214" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D214" s="2" t="s">
-        <v>744</v>
+      <c r="D214" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>908</v>
@@ -10889,11 +11168,11 @@
       <c r="B215" t="s">
         <v>595</v>
       </c>
-      <c r="C215" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>699</v>
+      <c r="C215" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>909</v>
@@ -10918,8 +11197,8 @@
       <c r="C216" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>699</v>
+      <c r="D216" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>910</v>
@@ -10944,8 +11223,8 @@
       <c r="C217" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D217" s="2" t="s">
-        <v>744</v>
+      <c r="D217" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>911</v>
@@ -10967,11 +11246,11 @@
       <c r="B218" t="s">
         <v>604</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>699</v>
+      <c r="C218" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>912</v>
@@ -10986,29 +11265,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="19">
-      <c r="A219">
+    <row r="219" spans="1:8" s="7" customFormat="1" ht="19" customHeight="1">
+      <c r="A219" s="7">
         <v>218</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B219" s="7" t="s">
         <v>1081</v>
       </c>
-      <c r="C219" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="E219" s="2" t="s">
+      <c r="C219" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D219" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E219" s="9" t="s">
         <v>913</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F219" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="G219" s="4">
+      <c r="G219" s="10">
         <v>46073</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="7">
         <v>1</v>
       </c>
     </row>
@@ -11045,8 +11324,8 @@
       <c r="B221" t="s">
         <v>613</v>
       </c>
-      <c r="C221" s="2" t="s">
-        <v>687</v>
+      <c r="C221" s="5" t="s">
+        <v>1127</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>688</v>
@@ -11100,8 +11379,8 @@
       <c r="C223" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>683</v>
+      <c r="D223" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>917</v>
@@ -11126,8 +11405,8 @@
       <c r="C224" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>699</v>
+      <c r="D224" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>918</v>
@@ -11152,8 +11431,8 @@
       <c r="C225" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>699</v>
+      <c r="D225" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>918</v>
@@ -11178,8 +11457,8 @@
       <c r="C226" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>699</v>
+      <c r="D226" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>919</v>
@@ -11204,8 +11483,8 @@
       <c r="C227" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>699</v>
+      <c r="D227" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>920</v>
@@ -11230,8 +11509,8 @@
       <c r="C228" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>744</v>
+      <c r="D228" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>921</v>
@@ -11256,8 +11535,8 @@
       <c r="C229" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>699</v>
+      <c r="D229" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>922</v>
@@ -11282,8 +11561,8 @@
       <c r="C230" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>699</v>
+      <c r="D230" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>923</v>
@@ -11308,8 +11587,8 @@
       <c r="C231" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>744</v>
+      <c r="D231" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>924</v>
@@ -11334,8 +11613,8 @@
       <c r="C232" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>744</v>
+      <c r="D232" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>925</v>
@@ -11360,8 +11639,8 @@
       <c r="C233" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>744</v>
+      <c r="D233" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>926</v>
@@ -11386,8 +11665,8 @@
       <c r="C234" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>683</v>
+      <c r="D234" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>927</v>
@@ -11438,8 +11717,8 @@
       <c r="C236" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>744</v>
+      <c r="D236" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>929</v>
@@ -11464,8 +11743,8 @@
       <c r="C237" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>683</v>
+      <c r="D237" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>930</v>
@@ -11490,8 +11769,8 @@
       <c r="C238" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D238" s="2" t="s">
-        <v>683</v>
+      <c r="D238" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>931</v>
@@ -11516,8 +11795,8 @@
       <c r="C239" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>683</v>
+      <c r="D239" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>932</v>
@@ -11542,8 +11821,8 @@
       <c r="C240" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>699</v>
+      <c r="D240" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>933</v>
@@ -11591,11 +11870,11 @@
       <c r="B242" t="s">
         <v>670</v>
       </c>
-      <c r="C242" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>691</v>
+      <c r="C242" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>935</v>
@@ -11620,8 +11899,8 @@
       <c r="C243" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>699</v>
+      <c r="D243" s="6" t="s">
+        <v>1124</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>936</v>
@@ -11672,8 +11951,8 @@
       <c r="C245" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>744</v>
+      <c r="D245" s="5" t="s">
+        <v>1128</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>938</v>
@@ -11698,8 +11977,8 @@
       <c r="C246" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>683</v>
+      <c r="D246" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>939</v>
@@ -11747,8 +12026,8 @@
       <c r="B248" t="s">
         <v>1014</v>
       </c>
-      <c r="C248" t="s">
-        <v>1015</v>
+      <c r="C248" s="2" t="s">
+        <v>693</v>
       </c>
       <c r="D248" t="s">
         <v>688</v>
@@ -11773,11 +12052,11 @@
       <c r="B249" t="s">
         <v>1086</v>
       </c>
-      <c r="C249" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D249" t="s">
-        <v>1020</v>
+      <c r="C249" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E249" t="s">
         <v>1021</v>
@@ -11799,11 +12078,11 @@
       <c r="B250" t="s">
         <v>1087</v>
       </c>
-      <c r="C250" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D250" t="s">
-        <v>1020</v>
+      <c r="C250" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>1129</v>
       </c>
       <c r="E250" t="s">
         <v>1025</v>
@@ -11826,10 +12105,10 @@
         <v>1088</v>
       </c>
       <c r="C251" t="s">
-        <v>1028</v>
+        <v>1126</v>
       </c>
       <c r="D251" t="s">
-        <v>699</v>
+        <v>1124</v>
       </c>
       <c r="E251" t="s">
         <v>1029</v>
@@ -11844,41 +12123,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
-      <c r="A252">
-        <v>251</v>
-      </c>
-      <c r="B252" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C252" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D252" t="s">
-        <v>699</v>
-      </c>
-      <c r="E252" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F252" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G252" s="4">
-        <v>46094</v>
-      </c>
-      <c r="H252">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:H251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N252"/>
+  <dimension ref="A1:N251"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -20005,7 +20260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="19">
+    <row r="219" spans="1:12" ht="95">
       <c r="A219">
         <v>218</v>
       </c>
@@ -21257,11 +21512,6 @@
       </c>
       <c r="L251">
         <v>1</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12">
-      <c r="B252" t="s">
-        <v>1031</v>
       </c>
     </row>
   </sheetData>

--- a/storybook_meta.xlsx
+++ b/storybook_meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cohue/Desktop/Files/10000shelf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B40148C-BE90-D848-959E-BAAE3A019EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEFAE62-6B51-C948-A7FE-195CF0E467F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="28800" windowHeight="15440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="storybooks_ai" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4596" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4805" uniqueCount="1175">
   <si>
     <t>id</t>
   </si>
@@ -4498,6 +4498,1818 @@
     <t>고사성어/속담</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빛나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끈기와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성장의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3-UP</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/19908ce6c412</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>과학기술인재들이 3-UP 운동과 '자주해' 정신 훈련을 통해 성과를 내고 꿈을 펼쳐나가는
+ 과정을 담은 15세 이상의 예비 및 현직 과학기술인재를 위한 수채화풍 스토리북</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>대학생이상</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛과 구도의 미학: 30년의 기록</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/efec20d272b8</t>
+  </si>
+  <si>
+    <t>30년 베테랑 사진작가와 함께 서울의 명소를 돌며 5가지 핵심 사진 기술을 배우는 
+과정을 담은, 사진에 관심 있는 청소년 및 성인을 위한 수채화풍 스토리북</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>청소년 이상</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>가장 정교한 언어, 숫자</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/7104dc26593a</t>
+  </si>
+  <si>
+    <t>수학, 언어학, 양자철학의 관점에서 숫자가 가장 정확한 언어임을 탐구하고, 한자 문화권 
+언어의 모호성을 비판적으로 분석하며 논리적 사고를 위한 언어 발전의 중요성을 다룬 15세 이상 독자를 위한 스토리북</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기계발</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 마음의 보물찾기: 4무량심 명상 여행</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준우의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세탁소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>: 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사무량심)</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리 뇌 속의 작은 왕, 아미 (아미그달라,겁대가리)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>소대가리가 되는 길: 회향(廻向)의 노래</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인생의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고스톱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멈춤과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나아감의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전략</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노트</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지혜의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치유하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신비로운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음악의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달빛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건네준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것들</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/1ee24268d8a7</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/570a415fdfe4</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/4ae05fea371b</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/254080ecd8ce</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/f2f3c8d61405</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/8a0d1549c27f</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/d0f4bec1bb54</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>사무량심 명상의 이론과 실천법을 통해 한 달간의 템플스테이에서 마음의 
+평화를 찾아가는 10세 독자를 위한 스토리북</t>
+  </si>
+  <si>
+    <t>친구와 싸워 속상해하던 10세 준우가 한 달간의 템플스테이를 통해 각주보살님께 
+'사무량심 명상'의 4단계를 배우며 미움을 평온으로 바꾸고 진정한 마음의 성장을 이루는</t>
+  </si>
+  <si>
+    <t>우리 뇌 속에서 공포를 관리하며 우리를 지켜주는 '작은 왕' 편도체(아미그달라)에 대한 이야기를 5세 아이들이 이해하기 쉽게 수채화풍으로 구성했습니다. 이 스토리북은 제공해 주신 복잡한 과학적 내용을 아이들의 눈높이에 맞게 각색</t>
+  </si>
+  <si>
+    <t>각성보살님이 '소대가리'와 '회향'이라는 독특한 비유를 통해 대학생들에게 
+진정한  성장의 의미와 수행의 단계를 따뜻한 수채화풍으로 들려주는 이야기</t>
+  </si>
+  <si>
+    <t>대학생 독자를 위해 인생의 고비마다 스스로 판단하고 결정할 수 있는 지혜를 
+담은 '고스톱 게임' 스토리북을 만들었습니다. 손자병법의 도천지장법과 세 가지 실천 원칙을 통해 철저한 준비의 중요성을 클레이 아트 스타일로 생생하게 담아냈으며</t>
+  </si>
+  <si>
+    <t>음악과 명상을 통해 일상의 불안과 스트레스를 해소하고 마음의 평화를 
+찾아가는 과정을 담은 9~16세 어린이를 위한 스토리북을 제작했습니다. 3D 디즈니/픽사 스타일의 생동감 넘치는 장면들과 함께 마음을 정화하는 특별한 여정</t>
+  </si>
+  <si>
+    <t>현대적으로 재해석된 '해와 달이 된 오누이' 이야기를 통해 진정한 나눔과 
+성장의 메시지를 담았으며, 중고등 및 고학년 독자들을 위한 깊이 있는 통찰</t>
+  </si>
+  <si>
+    <t>어린이</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>대학생</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>희언자연(稀言自然): 침묵이 빚어낸 큰 울림</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gemini.google.com/share/451eef2d1806</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>노자의 도덕경 23장 '희언 자연'의 가르침을 통해, 말이 적을수록 자연의 섭리에 가까워지
+고 마음이 비워진다는 지혜를 담은 대학생 및 성인 대상의 스토리북을 제작했습니다. 첨부해주신 이미지와 상세한 설정을 바탕으로 클레이아트 풍의 삽화와 함께 구성</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>속담편 (고사성어)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>30년 베테랑 사진작가와 서울 명소를 돌며 5가지 핵심 촬영 기술을 전수받는 여정 이야기</t>
+  </si>
+  <si>
+    <t>초등학생</t>
+  </si>
+  <si>
+    <t>아동</t>
+  </si>
+  <si>
+    <t>소대가리와 회향이라는 독특한 비유를 통해 진정한 성장의 의미와 수행 단계를 전하는 따뜻한 이야기</t>
+  </si>
+  <si>
+    <t>손자병법의 지혜를 고스톱 게임에 비유하여 인생의 고비마다 스스로 결정하는 법을 배우는 이야기</t>
+  </si>
+  <si>
+    <t>음악과 명상을 통해 일상의 스트레스를 해소하고 마음을 정화하며 평화를 찾아가는 여정 이야기</t>
+  </si>
+  <si>
+    <t>'해와 달이 된 오누이'를 현대적으로 재해석하여 나눔과 성장의 메시지를 깊이 있게 담아낸 이야기</t>
+  </si>
+  <si>
+    <t>고사성어/속담</t>
+  </si>
+  <si>
+    <t>노자 도덕경의 가르침을 통해 말이 적을수록 자연의 섭리에 가까워진다는 비움의 지혜 이야기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수학과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양자철학의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관점에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정확성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐구하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>논리적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사고를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>언어의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중요성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다룬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>사무량심 명상의 이론과 실천법을 통해 한 달간의 템플스테이에서 마음의 
+평화를 찾아가는 10세 독자를 위한 스토리북</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>템플스테이에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사무량심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진정한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평화를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾아가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달간의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구와 싸워 속상해하던 10세 준우가 한 달간의 템플스테이를 통해 각주보살님께 
+'사무량심 명상'의 4단계를 배우며 미움을 평온으로 바꾸고 진정한 마음의 성장을 이루는</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>친구와의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갈등을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사무량심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단계로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>풀어내며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미움을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평온으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바꾸는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준우의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리 뇌 속에서 공포를 관리하며 우리를 지켜주는 '작은 왕' 편도체(아미그달라)에 대한 이야기를 5세 아이들이 이해하기 쉽게 수채화풍으로 구성했습니다. 이 스토리북은 제공해 주신 복잡한 과학적 내용을 아이들의 눈높이에 맞게 각색</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뇌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공포를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>편도체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아미</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역할을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈높이에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들려주는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이야기</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준우의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세탁소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>: 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>큰마음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리 뇌 속의 작은 왕, 아미</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-UP 운동과 '자주해' 정신을 통해 성과를 내고 꿈을 펼치는 과학기술인재들의 성장 이야기</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4506,7 +6318,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4685,6 +6497,40 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -5112,7 +6958,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5129,6 +6975,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5222,8 +7086,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC114CC7-8A8E-5E46-8BF3-231BE583EA49}" name="표1" displayName="표1" ref="A1:H237" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H237" xr:uid="{6683F5E3-6C8D-C242-AB27-2C3142AF2489}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FC114CC7-8A8E-5E46-8BF3-231BE583EA49}" name="표1" displayName="표1" ref="A1:H248" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H248" xr:uid="{6683F5E3-6C8D-C242-AB27-2C3142AF2489}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3522E6B6-B2A4-8042-8945-FBB72B2554F5}" name="id" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{143FA870-96F6-F445-8D57-BD531367CF47}" name="title" dataDxfId="6"/>
@@ -5535,7 +7399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -12070,9 +13934,306 @@
         <v>1</v>
       </c>
     </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="6">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C252" t="s">
+        <v>684</v>
+      </c>
+      <c r="D252" t="s">
+        <v>691</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G252" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="6">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C253" t="s">
+        <v>684</v>
+      </c>
+      <c r="D253" t="s">
+        <v>691</v>
+      </c>
+      <c r="E253" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G253" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="6">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C254" t="s">
+        <v>684</v>
+      </c>
+      <c r="D254" t="s">
+        <v>691</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G254" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="6">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C255" t="s">
+        <v>689</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E255" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G255" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="6">
+        <v>255</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C256" t="s">
+        <v>689</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G256" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="6">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C257" t="s">
+        <v>683</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E257" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G257" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" s="6">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C258" t="s">
+        <v>690</v>
+      </c>
+      <c r="D258" t="s">
+        <v>691</v>
+      </c>
+      <c r="E258" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F258" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G258" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" s="6">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C259" t="s">
+        <v>684</v>
+      </c>
+      <c r="D259" t="s">
+        <v>691</v>
+      </c>
+      <c r="E259" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G259" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="6">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C260" t="s">
+        <v>689</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G260" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="6">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C261" t="s">
+        <v>686</v>
+      </c>
+      <c r="D261" t="s">
+        <v>685</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G261" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="6">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D262" t="s">
+        <v>691</v>
+      </c>
+      <c r="E262" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G262" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H262">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F252" r:id="rId1" xr:uid="{8BBB2E4D-7728-6B4B-A8BC-5D283E6D5A30}"/>
+    <hyperlink ref="F255" r:id="rId2" xr:uid="{2475A061-90B0-EE4D-A0C8-4E84541FF576}"/>
+    <hyperlink ref="F257" r:id="rId3" xr:uid="{68551E99-C109-904C-B028-478B06986AF2}"/>
+    <hyperlink ref="F258" r:id="rId4" xr:uid="{ECA0A7F7-F93B-A144-891B-72F5FA5A7453}"/>
+    <hyperlink ref="F259" r:id="rId5" xr:uid="{6B2916E0-FF19-6245-BA6D-07C56BBB43A1}"/>
+    <hyperlink ref="F260" r:id="rId6" xr:uid="{2888F12B-6C7F-A44B-AC42-94DA3B0A0BEF}"/>
+    <hyperlink ref="F261" r:id="rId7" xr:uid="{3BA38C9F-A4B4-3749-BCA9-83A534998FEF}"/>
+    <hyperlink ref="F256" r:id="rId8" xr:uid="{427BECEA-9C03-804C-A81B-A68165AAB96A}"/>
+    <hyperlink ref="F262" r:id="rId9" xr:uid="{CABB6E00-4182-F841-8515-BA187B116F78}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -12080,7 +14241,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N251"/>
+  <dimension ref="A1:N262"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -20207,41 +22368,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="95">
-      <c r="A219">
+    <row r="219" spans="1:12" s="6" customFormat="1">
+      <c r="A219" s="6">
         <v>218</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B219" s="6" t="s">
         <v>1064</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="D219" s="5" t="s">
+      <c r="D219" s="9" t="s">
         <v>1110</v>
       </c>
-      <c r="E219" t="s">
+      <c r="E219" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="F219" s="5" t="s">
+      <c r="F219" s="9" t="s">
         <v>1106</v>
       </c>
-      <c r="G219" t="s">
+      <c r="G219" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="H219" s="2" t="s">
+      <c r="H219" s="10" t="s">
         <v>902</v>
       </c>
-      <c r="I219" t="s">
+      <c r="I219" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="J219" t="s">
+      <c r="J219" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="K219" s="4">
+      <c r="K219" s="7">
         <v>46073</v>
       </c>
-      <c r="L219">
+      <c r="L219" s="6">
         <v>1</v>
       </c>
     </row>
@@ -21347,123 +23508,552 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:12">
-      <c r="A249">
+    <row r="249" spans="1:12" s="6" customFormat="1">
+      <c r="A249" s="6">
         <v>248</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B249" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="C249" t="s">
+      <c r="C249" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="D249" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="E249" t="s">
+      <c r="E249" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="F249" s="5" t="s">
+      <c r="F249" s="9" t="s">
         <v>1112</v>
       </c>
-      <c r="G249" t="s">
+      <c r="G249" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="H249" t="s">
+      <c r="H249" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="I249" t="s">
+      <c r="I249" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="J249" t="s">
+      <c r="J249" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="K249" s="4">
+      <c r="K249" s="7">
         <v>46094</v>
       </c>
-      <c r="L249">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12">
-      <c r="A250">
+      <c r="L249" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" s="6" customFormat="1">
+      <c r="A250" s="6">
         <v>249</v>
       </c>
-      <c r="B250" t="s">
+      <c r="B250" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="C250" t="s">
+      <c r="C250" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="D250" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="E250" t="s">
+      <c r="E250" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="F250" s="5" t="s">
+      <c r="F250" s="9" t="s">
         <v>1112</v>
       </c>
-      <c r="G250" t="s">
+      <c r="G250" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="H250" t="s">
+      <c r="H250" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="I250" t="s">
+      <c r="I250" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="J250" t="s">
+      <c r="J250" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="K250" s="4">
+      <c r="K250" s="7">
         <v>46094</v>
       </c>
-      <c r="L250">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="251" spans="1:12">
-      <c r="A251">
+      <c r="L250" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" s="6" customFormat="1">
+      <c r="A251" s="6">
         <v>250</v>
       </c>
-      <c r="B251" t="s">
+      <c r="B251" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="C251" t="s">
+      <c r="C251" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="D251" t="s">
+      <c r="D251" s="6" t="s">
         <v>1109</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E251" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="F251" t="s">
+      <c r="F251" s="6" t="s">
         <v>1107</v>
       </c>
-      <c r="G251" t="s">
+      <c r="G251" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="H251" t="s">
+      <c r="H251" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="I251" t="s">
+      <c r="I251" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="J251" t="s">
+      <c r="J251" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="K251" s="4">
+      <c r="K251" s="7">
         <v>46094</v>
       </c>
-      <c r="L251">
+      <c r="L251" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" s="6" customFormat="1">
+      <c r="A252" s="6">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D252" t="s">
+        <v>684</v>
+      </c>
+      <c r="E252" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F252" t="s">
+        <v>691</v>
+      </c>
+      <c r="G252" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I252" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J252" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K252" s="7">
+        <v>46094</v>
+      </c>
+      <c r="L252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" s="6" customFormat="1">
+      <c r="A253" s="6">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D253" t="s">
+        <v>684</v>
+      </c>
+      <c r="E253" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F253" t="s">
+        <v>691</v>
+      </c>
+      <c r="G253" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H253" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I253" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J253" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K253" s="7">
+        <v>46094</v>
+      </c>
+      <c r="L253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" s="6" customFormat="1">
+      <c r="A254" s="6">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D254" t="s">
+        <v>684</v>
+      </c>
+      <c r="E254" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F254" t="s">
+        <v>691</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H254" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I254" t="s">
+        <v>1126</v>
+      </c>
+      <c r="J254" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K254" s="7">
+        <v>46094</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" s="6" customFormat="1">
+      <c r="A255" s="6">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D255" t="s">
+        <v>689</v>
+      </c>
+      <c r="E255" t="s">
+        <v>932</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G255" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H255" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I255" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J255" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K255" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" s="6" customFormat="1">
+      <c r="A256" s="6">
+        <v>255</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D256" t="s">
+        <v>689</v>
+      </c>
+      <c r="E256" t="s">
+        <v>932</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G256" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H256" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I256" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J256" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K256" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" s="6" customFormat="1">
+      <c r="A257" s="6">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D257" t="s">
+        <v>683</v>
+      </c>
+      <c r="E257" t="s">
+        <v>932</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G257" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H257" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I257" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J257" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K257" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" s="6" customFormat="1">
+      <c r="A258" s="6">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D258" t="s">
+        <v>690</v>
+      </c>
+      <c r="E258" t="s">
+        <v>932</v>
+      </c>
+      <c r="F258" t="s">
+        <v>691</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I258" t="s">
+        <v>1145</v>
+      </c>
+      <c r="J258" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K258" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" s="6" customFormat="1">
+      <c r="A259" s="6">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D259" t="s">
+        <v>684</v>
+      </c>
+      <c r="E259" t="s">
+        <v>932</v>
+      </c>
+      <c r="F259" t="s">
+        <v>691</v>
+      </c>
+      <c r="G259" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I259" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K259" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" s="6" customFormat="1">
+      <c r="A260" s="6">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D260" t="s">
+        <v>689</v>
+      </c>
+      <c r="E260" t="s">
+        <v>932</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H260" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I260" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J260" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K260" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" s="6" customFormat="1">
+      <c r="A261" s="6">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D261" t="s">
+        <v>686</v>
+      </c>
+      <c r="E261" t="s">
+        <v>932</v>
+      </c>
+      <c r="F261" t="s">
+        <v>685</v>
+      </c>
+      <c r="G261" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H261" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I261" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J261" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K261" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" s="6" customFormat="1">
+      <c r="A262" s="6">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E262" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F262" t="s">
+        <v>691</v>
+      </c>
+      <c r="G262" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H262" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I262" t="s">
+        <v>1153</v>
+      </c>
+      <c r="J262" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K262" s="7">
+        <v>46095</v>
+      </c>
+      <c r="L262">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M251" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J252" r:id="rId1" xr:uid="{E043EC2D-F72C-9442-BABC-68BCC41C59D3}"/>
+    <hyperlink ref="J255" r:id="rId2" xr:uid="{F8563745-8E9F-4147-BFBE-B8B40E1F1436}"/>
+    <hyperlink ref="J257" r:id="rId3" xr:uid="{1E544F86-0CBC-6C4F-8846-8B95F3FFF923}"/>
+    <hyperlink ref="J258" r:id="rId4" xr:uid="{86F411AF-E903-5645-A0EF-25A5E59A66FD}"/>
+    <hyperlink ref="J259" r:id="rId5" xr:uid="{CE729963-D5D3-A349-B05A-517DEDC880D9}"/>
+    <hyperlink ref="J260" r:id="rId6" xr:uid="{43D8DEAE-ACC2-6C4F-B3B2-247344B264DF}"/>
+    <hyperlink ref="J261" r:id="rId7" xr:uid="{94E1B1BF-C860-8C41-B8F3-097513C0B83B}"/>
+    <hyperlink ref="J256" r:id="rId8" xr:uid="{EDD8CAC5-EA7D-1445-B633-A82559EB3465}"/>
+    <hyperlink ref="J262" r:id="rId9" xr:uid="{6DE8D6C9-E53B-1742-94E5-E587FB881119}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -21471,7 +24061,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E845D2-1ABF-E54D-BB32-A1AE5C43F463}">
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -21486,7 +24076,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -27478,11 +30068,308 @@
         <v>0</v>
       </c>
     </row>
+    <row r="238" spans="1:8" s="6" customFormat="1">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G238" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H238" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" s="6" customFormat="1">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E239" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G239" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H239" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" s="6" customFormat="1">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G240" s="7">
+        <v>46094</v>
+      </c>
+      <c r="H240" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" s="6" customFormat="1">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C241" t="s">
+        <v>932</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G241" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H241" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" s="6" customFormat="1">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C242" t="s">
+        <v>932</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G242" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H242" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" s="6" customFormat="1">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C243" t="s">
+        <v>932</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E243" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G243" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H243" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" s="6" customFormat="1">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C244" t="s">
+        <v>932</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E244" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G244" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H244" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" s="6" customFormat="1">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C245" t="s">
+        <v>932</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E245" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G245" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H245" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" s="6" customFormat="1">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C246" t="s">
+        <v>932</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E246" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F246" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G246" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H246" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" s="6" customFormat="1">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C247" t="s">
+        <v>932</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E247" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F247" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G247" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H247" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" s="6" customFormat="1">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F248" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G248" s="7">
+        <v>46095</v>
+      </c>
+      <c r="H248" s="6">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F238" r:id="rId1" xr:uid="{05329043-4787-734D-A4EA-49308B7F57B2}"/>
+    <hyperlink ref="F241" r:id="rId2" xr:uid="{7E3723AE-ED21-C14B-B2F9-7F635AB85BEA}"/>
+    <hyperlink ref="F243" r:id="rId3" xr:uid="{FF9C92D6-B24F-9F4A-979A-30900675D260}"/>
+    <hyperlink ref="F244" r:id="rId4" xr:uid="{746473D4-FDA2-B74E-AD43-4AC7A7B2A461}"/>
+    <hyperlink ref="F245" r:id="rId5" xr:uid="{05BEA868-5BD4-CA43-9EB0-0A738D2EECD6}"/>
+    <hyperlink ref="F246" r:id="rId6" xr:uid="{9647415C-5C04-0B41-92E8-E9BB4822C33E}"/>
+    <hyperlink ref="F247" r:id="rId7" xr:uid="{48865B7F-3006-344E-B245-D7E05EC71EBF}"/>
+    <hyperlink ref="F242" r:id="rId8" xr:uid="{0E3CE307-3823-4546-B853-B5BF419B205F}"/>
+    <hyperlink ref="F248" r:id="rId9" xr:uid="{B6288B6A-C770-A04D-8B22-301271AB93B3}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>